--- a/artfynd/A 33487-2025 artfynd.xlsx
+++ b/artfynd/A 33487-2025 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>126379815</v>
       </c>
       <c r="B8" t="n">
-        <v>100551</v>
+        <v>100560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>126379817</v>
       </c>
       <c r="B9" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>126379818</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>126379813</v>
       </c>
       <c r="B11" t="n">
-        <v>100551</v>
+        <v>100560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>126379812</v>
       </c>
       <c r="B12" t="n">
-        <v>100551</v>
+        <v>100560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>126379814</v>
       </c>
       <c r="B13" t="n">
-        <v>100551</v>
+        <v>100560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>126379811</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126379816</v>
       </c>
       <c r="B15" t="n">
-        <v>100551</v>
+        <v>100560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
